--- a/public/magnolia/kitchen.xlsx
+++ b/public/magnolia/kitchen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/magnolia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6DBE30-F257-2041-8F47-D2AE64C7A3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B465FCA-3F1F-F84E-B4AB-3D650289345C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1540" yWindow="1480" windowWidth="16380" windowHeight="14480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -259,12 +259,6 @@
   </si>
   <si>
     <t>უდონი ორაგულით</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breakfast </t>
-  </si>
-  <si>
-    <t xml:space="preserve">საუზმე დილის </t>
   </si>
   <si>
     <t>Обед</t>
@@ -526,6 +520,12 @@
   </si>
   <si>
     <t>Pancakes with condensed milk and banana</t>
+  </si>
+  <si>
+    <t>Breakfast</t>
+  </si>
+  <si>
+    <t>საუზმე დილის</t>
   </si>
 </sst>
 </file>
@@ -1175,25 +1175,25 @@
     </row>
     <row r="2" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -1328,13 +1328,13 @@
         <v>17</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G2" s="29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I2" s="11" t="str">
         <f t="shared" ref="I2:I14" si="0">LOWER($B2)</f>
@@ -1360,13 +1360,13 @@
         <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I3" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1379,26 +1379,26 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="23">
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I4" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1424,13 +1424,13 @@
         <v>16</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I5" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1456,13 +1456,13 @@
         <v>20</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I6" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1488,13 +1488,13 @@
         <v>17</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I7" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1520,13 +1520,13 @@
         <v>19</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I8" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1552,13 +1552,13 @@
         <v>22</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I9" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1604,13 +1604,13 @@
         <v>22</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I10" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1656,13 +1656,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I11" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1744,7 +1744,7 @@
         <v>64</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>65</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="14" spans="1:30" ht="19" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="24">
@@ -29451,13 +29451,13 @@
         <v>25</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I2" s="11" t="str">
         <f t="shared" ref="I2:I16" si="0">LOWER($B2)</f>
@@ -29476,20 +29476,20 @@
         <v>46</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="23">
         <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I3" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29502,26 +29502,26 @@
     </row>
     <row r="4" spans="1:30" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="23">
         <v>21</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I4" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29534,26 +29534,26 @@
     </row>
     <row r="5" spans="1:30" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="23">
         <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I5" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29579,13 +29579,13 @@
         <v>28</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I6" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29610,13 +29610,13 @@
         <v>22</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I7" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29661,13 +29661,13 @@
         <v>18</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I8" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29712,13 +29712,13 @@
         <v>26</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I9" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29763,13 +29763,13 @@
         <v>21</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I10" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29814,13 +29814,13 @@
         <v>22</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I11" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29866,13 +29866,13 @@
         <v>18</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I12" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29918,13 +29918,13 @@
         <v>18</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I13" s="11" t="str">
         <f t="shared" si="0"/>
@@ -29957,13 +29957,13 @@
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E14" s="24">
         <v>6</v>
